--- a/recipes/onion-garlic-free-indian/focus-states/14-rajasthan/excel/rajasthan-recipes.xlsx
+++ b/recipes/onion-garlic-free-indian/focus-states/14-rajasthan/excel/rajasthan-recipes.xlsx
@@ -104,7 +104,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="009A3412"/>
-      <sz val="16"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="19">
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -358,6 +358,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1465,7 +1468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1477,7 +1480,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Papad ki sabzi (Rajasthani, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Papad ki sabzi (Rajasthani, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1487,7 +1490,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan kitchen  ·  Side  ·  Marwari, Mewari and Jain vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Rajasthan  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1507,44 +1510,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -1692,34 +1695,239 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="42" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Temper cumin hing. Add yogurt spices on low. Add papad pieces. Simmer 5 min.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Temper cumin hing. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Add yogurt spices on low. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Add papad pieces. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Simmer 5 min. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 142  ·  Protein 10 g  ·  Carbs 21 g  ·  Fat 2 g  ·  Fibre 5 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Papad ki sabzi (Rajasthani, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Bring yogurt to a simmer gently and stir; a rolling boil can split it.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1733,7 +1941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1745,7 +1953,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Rajasthani kadhi (besan, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Rajasthani kadhi (besan, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1755,7 +1963,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan kitchen  ·  Side  ·  Marwari, Mewari and Jain vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Rajasthan  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1775,44 +1983,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 10 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -1996,13 +2204,13 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Whisk yogurt-besan. Simmer till thick.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
@@ -2014,31 +2222,223 @@
       </c>
       <c r="B23" s="30" t="inlineStr">
         <is>
-          <t>Temper whole spices in ghee. Pour over kadhi.</t>
+          <t>Cut vegetables to even size so they cook together.</t>
         </is>
       </c>
       <c r="C23" s="31" t="n"/>
       <c r="D23" s="31" t="n"/>
     </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Whisk yogurt-besan. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Simmer till thick. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Temper whole spices in ghee. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Pour over kadhi. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>kcal 62  ·  Protein 3 g  ·  Carbs 7 g  ·  Fat 2 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>For Rajasthani kadhi (besan, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Bring yogurt to a simmer gently and stir; a rolling boil can split it. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B40" s="50" t="n"/>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="33">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2052,7 +2452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2064,7 +2464,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Aloo pyaz-free rassa (tomato potato)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Aloo pyaz-free rassa (tomato potato)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2074,7 +2474,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan kitchen  ·  Side  ·  Marwari, Mewari and Jain vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Rajasthan  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2094,44 +2494,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 15 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -2297,35 +2697,253 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="42" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Temper spices. Tomato. Potatoes. Water. Simmer till potatoes melt into gravy.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Temper spices. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Tomato. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Potatoes. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Water. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Simmer till potatoes melt into gravy. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>kcal 20  ·  Protein 1 g  ·  Carbs 4 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>For Aloo pyaz-free rassa (tomato potato): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B40" s="50" t="n"/>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="33">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2339,7 +2957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2351,7 +2969,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Bajra roti (pearl millet, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Bajra roti (pearl millet, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2361,7 +2979,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan kitchen  ·  Bread  ·  Marwari, Mewari and Jain vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Rajasthan  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2381,44 +2999,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 15 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -2530,32 +3148,224 @@
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="46" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="54" customHeight="1">
       <c r="A18" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Knead hot-water dough. Pat rotis. Cook on tawa. Ghee.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="49" t="n"/>
     </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Knead hot-water dough. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Pat rotis. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Cook on tawa. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Ghee. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 713  ·  Protein 22 g  ·  Carbs 121 g  ·  Fat 16 g  ·  Fibre 20 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Bajra roti (pearl millet, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2569,7 +3379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2581,7 +3391,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Missi roti (besan-wheat, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Missi roti (besan-wheat, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2591,7 +3401,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan kitchen  ·  Bread  ·  Marwari, Mewari and Jain vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Rajasthan  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2611,44 +3421,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 15 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -2796,34 +3606,213 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="54" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Knead. Roll. Cook on tawa with ghee.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Knead. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Roll. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Cook on tawa with ghee. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 321  ·  Protein 14 g  ·  Carbs 61 g  ·  Fat 3 g  ·  Fibre 10 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Missi roti (besan-wheat, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2837,7 +3826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2849,7 +3838,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Baati (baked wheat balls)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Baati (baked wheat balls)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2859,7 +3848,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan kitchen  ·  Bread  ·  Marwari, Mewari and Jain vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Rajasthan  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2879,44 +3868,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>Prep 20 min · Cook 40 min</t>
         </is>
       </c>
     </row>
@@ -3046,46 +4035,225 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="42" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Knead stiff. Shape. Bake in clay tandoor or roast in heavy kadai 35–40 min.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel or clay pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="42" customHeight="1">
       <c r="A20" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B20" s="30" t="inlineStr">
         <is>
-          <t>Crack and soak in ghee.</t>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
         </is>
       </c>
       <c r="C20" s="31" t="n"/>
       <c r="D20" s="31" t="n"/>
     </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Knead stiff. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Shape. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="66" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Bake in clay tandoor or roast in heavy kadai 35–40 min. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Crack and soak in ghee. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 639  ·  Protein 11 g  ·  Carbs 65 g  ·  Fat 38 g  ·  Fibre 10 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Baati (baked wheat balls): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="29">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3099,7 +4267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3111,7 +4279,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Ghevar (disc jalebi, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Ghevar (disc jalebi, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3121,7 +4289,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan kitchen  ·  Sweet  ·  Marwari, Mewari and Jain vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Rajasthan  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3141,44 +4309,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>70 min</t>
+          <t>Prep 40 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -3308,13 +4476,13 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="42" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Make thin batter. Pour in circular motion into hot ghee to form honeycomb disc. Fry.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
@@ -3326,28 +4494,220 @@
       </c>
       <c r="B20" s="30" t="inlineStr">
         <is>
-          <t>Dip in syrup. Garnish pistachio.</t>
+          <t>Cut vegetables to even size so they cook together.</t>
         </is>
       </c>
       <c r="C20" s="31" t="n"/>
       <c r="D20" s="31" t="n"/>
     </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Make thin batter. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="66" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Pour in circular motion into hot ghee to form honeycomb disc. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Fry. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Dip in syrup. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Garnish pistachio. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 785  ·  Protein 8 g  ·  Carbs 120 g  ·  Fat 31 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Tree nuts · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Ghevar (disc jalebi, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Tree nuts; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="30">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3361,7 +4721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3373,7 +4733,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Churma (crushed baati sweet)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Churma (crushed baati sweet)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3383,7 +4743,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan kitchen  ·  Sweet  ·  Marwari, Mewari and Jain vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Rajasthan  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3403,44 +4763,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Prep 20 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -3588,34 +4948,213 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="42" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Fry crushed baati in ghee in kadai. Mix jaggery off heat. Cardamom, nuts.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Fry crushed baati in ghee in kadai. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Mix jaggery off heat. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Cardamom, nuts. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 521  ·  Protein 1 g  ·  Carbs 42 g  ·  Fat 39 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Churma (crushed baati sweet): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3629,7 +5168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3641,7 +5180,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Moong dal halwa (Marwari)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Moong dal halwa (Marwari)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3651,7 +5190,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan kitchen  ·  Sweet  ·  Marwari, Mewari and Jain vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Rajasthan  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3671,44 +5210,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>75 min</t>
+          <t>Prep 30 min · Cook 45 min</t>
         </is>
       </c>
     </row>
@@ -3856,47 +5395,226 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="42" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Roast dal paste in ghee till grainy and aromatic (long stir in kadai).</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="42" customHeight="1">
       <c r="A21" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B21" s="30" t="inlineStr">
         <is>
-          <t>Add milk then sugar. Cook till ghee separates. Garnish.</t>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
         </is>
       </c>
       <c r="C21" s="31" t="n"/>
       <c r="D21" s="31" t="n"/>
     </row>
+    <row r="22" ht="66" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Roast dal paste in ghee till grainy and aromatic (long stir in kadai). Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Add milk then sugar. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Cook till ghee separates. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Garnish. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 854  ·  Protein 20 g  ·  Carbs 106 g  ·  Fat 41 g  ·  Fibre 12 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Moong dal halwa (Marwari): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3910,7 +5628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3922,7 +5640,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Malpua (saffron, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Malpua (saffron, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3932,7 +5650,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan kitchen  ·  Dessert  ·  Marwari, Mewari and Jain vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Rajasthan  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3952,44 +5670,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 20 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -4101,32 +5819,211 @@
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="46" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="66" customHeight="1">
       <c r="A18" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Rest batter. Fry small pancakes. Soak in syrup.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="49" t="n"/>
     </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Rest batter. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Fry small pancakes. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Soak in syrup. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 292  ·  Protein 8 g  ·  Carbs 58 g  ·  Fat 2 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Malpua (saffron, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4404,7 +6301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4416,7 +6313,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Mawa kachori (sweet stuffed, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Mawa kachori (sweet stuffed, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4426,7 +6323,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan kitchen  ·  Dessert  ·  Marwari, Mewari and Jain vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Rajasthan  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4446,44 +6343,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>65 min</t>
+          <t>Prep 40 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -4613,33 +6510,212 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Stuff pastry with sweet mawa. Fry in kadai. Dip in syrup.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Stuff pastry with sweet mawa. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Fry in kadai. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Dip in syrup. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 967  ·  Protein 22 g  ·  Carbs 167 g  ·  Fat 21 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Mawa kachori (sweet stuffed, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="28">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4653,7 +6729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4665,7 +6741,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Rabdi (slow milk, clay optional)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Rabdi (slow milk, clay optional)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4675,7 +6751,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan kitchen  ·  Dessert  ·  Marwari, Mewari and Jain vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Rajasthan  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4695,44 +6771,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Hot or chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>Prep 10 min · Cook 50 min</t>
         </is>
       </c>
     </row>
@@ -4844,32 +6920,211 @@
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="46" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="66" customHeight="1">
       <c r="A18" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Reduce milk stirring. Sugar, saffron, nuts. Chill.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="49" t="n"/>
     </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Reduce milk stirring. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Sugar, saffron, nuts. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Chill. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot or chilled.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 393  ·  Protein 16 g  ·  Carbs 44 g  ·  Fat 18 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Rabdi (slow milk, clay optional): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot or chilled. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4883,7 +7138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4895,7 +7150,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Kachumber no onion (cucumber tomato)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Kachumber no onion (cucumber tomato)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4905,7 +7160,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan kitchen  ·  Salad  ·  Marwari, Mewari and Jain vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Rajasthan  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4925,44 +7180,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Prep 10 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5056,31 +7311,210 @@
       <c r="C16" s="46" t="n"/>
       <c r="D16" s="46" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="54" customHeight="1">
       <c r="A17" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="48" t="inlineStr">
         <is>
-          <t>Chop. Toss. No onion.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C17" s="49" t="n"/>
       <c r="D17" s="49" t="n"/>
     </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="48" t="inlineStr">
+        <is>
+          <t>Chop. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Toss. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>No onion. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 2  ·  Protein 0 g  ·  Carbs 0 g  ·  Fat 0 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Kachumber no onion (cucumber tomato): squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="26">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5094,7 +7528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5106,7 +7540,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Sprouted moth salad (matki, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Sprouted moth salad (matki, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5116,7 +7550,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan kitchen  ·  Salad  ·  Marwari, Mewari and Jain vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Rajasthan  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5136,44 +7570,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Prep 10 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5357,36 +7791,189 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="54" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Toss warm sprouts with dressing.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Toss warm sprouts with dressing. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 259  ·  Protein 16 g  ·  Carbs 48 g  ·  Fat 1 g  ·  Fibre 13 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Sprouted moth salad (matki, no onion): squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5400,7 +7987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5412,7 +7999,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Pomegranate-boondi raita salad</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Pomegranate-boondi raita salad</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5422,7 +8009,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan kitchen  ·  Salad  ·  Marwari, Mewari and Jain vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Rajasthan  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5442,44 +8029,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Prep 10 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5609,33 +8196,199 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="54" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Mix. Chill.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Mix. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Chill. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 104  ·  Protein 5 g  ·  Carbs 13 g  ·  Fat 4 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Pomegranate-boondi raita salad: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve in a steel or glass bowl. Stir at the pass so it is not split or settled. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="27">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -8199,7 +10952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8211,7 +10964,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Dal kachori (hing, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Dal kachori (hing, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8221,7 +10974,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan kitchen  ·  Starter  ·  Marwari, Mewari and Jain vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Rajasthan  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -8241,44 +10994,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>65 min</t>
+          <t>Prep 40 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -8498,64 +11251,282 @@
       <c r="C23" s="46" t="n"/>
       <c r="D23" s="46" t="n"/>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Grind dal coarse. Temper cumin, fennel, chilli, hing, amchur. Mix.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="42" customHeight="1">
       <c r="A25" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B25" s="30" t="inlineStr">
         <is>
-          <t>Knead atta with ghee and water. Stuff kachoris. Fry golden in kadai.</t>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
         </is>
       </c>
       <c r="C25" s="31" t="n"/>
       <c r="D25" s="31" t="n"/>
     </row>
-    <row r="26" ht="36" customHeight="1">
+    <row r="26" ht="54" customHeight="1">
       <c r="A26" s="47" t="n">
         <v>3</v>
       </c>
       <c r="B26" s="48" t="inlineStr">
         <is>
-          <t>Serve with imli chutney.</t>
+          <t>Heat fat in Steel kadhai for frying — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
         </is>
       </c>
       <c r="C26" s="49" t="n"/>
       <c r="D26" s="49" t="n"/>
     </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Grind dal coarse. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Temper cumin, fennel, chilli, hing, amchur. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Mix. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Knead atta with ghee and water. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Stuff kachoris. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>Fry golden in kadai. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+    </row>
+    <row r="33" ht="54" customHeight="1">
+      <c r="A33" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>Serve with imli chutney. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="n"/>
+      <c r="D33" s="31" t="n"/>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="B34" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C34" s="49" t="n"/>
+      <c r="D34" s="49" t="n"/>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="B35" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C35" s="31" t="n"/>
+      <c r="D35" s="31" t="n"/>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="47" t="n">
+        <v>13</v>
+      </c>
+      <c r="B36" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C36" s="49" t="n"/>
+      <c r="D36" s="49" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="n"/>
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="22" t="n"/>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>kcal 570  ·  Protein 29 g  ·  Carbs 113 g  ·  Fat 2 g  ·  Fibre 22 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+    </row>
+    <row r="41" ht="48" customHeight="1">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B41" s="26" t="n"/>
+      <c r="C41" s="26" t="n"/>
+      <c r="D41" s="26" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+    </row>
+    <row r="43" ht="72" customHeight="1">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>For Dal kachori (hing, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="n"/>
+      <c r="C43" s="26" t="n"/>
+      <c r="D43" s="26" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B44" s="52" t="n"/>
+      <c r="C44" s="52" t="n"/>
+      <c r="D44" s="52" t="n"/>
+    </row>
+    <row r="45" ht="64" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B45" s="50" t="n"/>
+      <c r="C45" s="50" t="n"/>
+      <c r="D45" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="38">
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A44:D44"/>
     <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -8569,7 +11540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8581,7 +11552,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Mirchi vada (stuffed chilli, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Mirchi vada (stuffed chilli, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8591,7 +11562,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan kitchen  ·  Starter  ·  Marwari, Mewari and Jain vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Rajasthan  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -8611,44 +11582,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 25 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -8814,48 +11785,240 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Stuff chillies with spiced potato. Dip in besan. Fry in kadai.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="42" customHeight="1">
       <c r="A22" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B22" s="30" t="inlineStr">
         <is>
-          <t>Serve with imli.</t>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet.</t>
         </is>
       </c>
       <c r="C22" s="31" t="n"/>
       <c r="D22" s="31" t="n"/>
     </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Steel kadhai for frying — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Stuff chillies with spiced potato. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Dip in besan. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Fry in kadai. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Serve with imli. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>kcal 194  ·  Protein 1 g  ·  Carbs 4 g  ·  Fat 20 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="72" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>For Mirchi vada (stuffed chilli, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="32">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -8869,7 +12032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8881,7 +12044,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Gatte ki tikki (steamed gram flour, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Gatte ki tikki (steamed gram flour, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8891,7 +12054,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan kitchen  ·  Starter  ·  Marwari, Mewari and Jain vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Rajasthan  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -8911,44 +12074,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 20 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -9132,13 +12295,13 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Knead besan dough. Roll cylinders. Steam 15 min in steamer. Slice.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel steamer and steel thali — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
@@ -9150,31 +12313,249 @@
       </c>
       <c r="B23" s="30" t="inlineStr">
         <is>
-          <t>Pan-sear slices on tawa in ghee. Serve with dahi.</t>
+          <t>Cut vegetables to even size so they cook together.</t>
         </is>
       </c>
       <c r="C23" s="31" t="n"/>
       <c r="D23" s="31" t="n"/>
     </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel steamer and steel thali — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Knead besan dough. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Roll cylinders. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Steam 15 min in steamer. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Slice. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Pan-sear slices on tawa in ghee. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Serve with dahi. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="n"/>
+      <c r="D33" s="31" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>kcal 254  ·  Protein 14 g  ·  Carbs 37 g  ·  Fat 5 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="48" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+    </row>
+    <row r="40" ht="72" customHeight="1">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>For Gatte ki tikki (steamed gram flour, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Bring yogurt to a simmer gently and stir; a rolling boil can split it. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B41" s="52" t="n"/>
+      <c r="C41" s="52" t="n"/>
+      <c r="D41" s="52" t="n"/>
+    </row>
+    <row r="42" ht="64" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B42" s="50" t="n"/>
+      <c r="C42" s="50" t="n"/>
+      <c r="D42" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="35">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9188,7 +12569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9200,7 +12581,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Dal baati (sattvic, no onion garlic)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Dal baati (sattvic, no onion garlic)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9210,7 +12591,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan kitchen  ·  Main  ·  Marwari, Mewari and Jain vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Rajasthan  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9230,44 +12611,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>80 min</t>
+          <t>Prep 30 min · Cook 50 min</t>
         </is>
       </c>
     </row>
@@ -9469,13 +12850,13 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="42" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Knead stiff dough. Shape baati. Bake on tandoor/clay or roast in heavy kadhai 35 min, turning.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
@@ -9487,45 +12868,263 @@
       </c>
       <c r="B24" s="30" t="inlineStr">
         <is>
-          <t>Cook dals with turmeric. Temper cumin, hing, tomato, ginger in kadai. Mix.</t>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
         </is>
       </c>
       <c r="C24" s="31" t="n"/>
       <c r="D24" s="31" t="n"/>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="54" customHeight="1">
       <c r="A25" s="47" t="n">
         <v>3</v>
       </c>
       <c r="B25" s="48" t="inlineStr">
         <is>
-          <t>Crack baati, soak in ghee, serve with dal.</t>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
         </is>
       </c>
       <c r="C25" s="49" t="n"/>
       <c r="D25" s="49" t="n"/>
     </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Knead stiff dough. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Shape baati. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="66" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Bake on tandoor/clay or roast in heavy kadhai 35 min, turning. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Cook dals with turmeric. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Temper cumin, hing, tomato, ginger in kadai. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Mix. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>Crack baati, soak in ghee, serve with dal. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="B33" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="49" t="n"/>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C34" s="31" t="n"/>
+      <c r="D34" s="31" t="n"/>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="47" t="n">
+        <v>13</v>
+      </c>
+      <c r="B35" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C35" s="49" t="n"/>
+      <c r="D35" s="49" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="n"/>
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="22" t="n"/>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>kcal 668  ·  Protein 16 g  ·  Carbs 67 g  ·  Fat 39 g  ·  Fibre 12 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+    </row>
+    <row r="40" ht="48" customHeight="1">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+    </row>
+    <row r="42" ht="72" customHeight="1">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>For Dal baati (sattvic, no onion garlic): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B42" s="26" t="n"/>
+      <c r="C42" s="26" t="n"/>
+      <c r="D42" s="26" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B43" s="52" t="n"/>
+      <c r="C43" s="52" t="n"/>
+      <c r="D43" s="52" t="n"/>
+    </row>
+    <row r="44" ht="64" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B44" s="50" t="n"/>
+      <c r="C44" s="50" t="n"/>
+      <c r="D44" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="37">
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9539,7 +13138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9551,7 +13150,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Gatte ki sabzi (no onion garlic)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Gatte ki sabzi (no onion garlic)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9561,7 +13160,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan kitchen  ·  Main  ·  Marwari, Mewari and Jain vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Rajasthan  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9581,44 +13180,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>55 min</t>
+          <t>Prep 25 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -9802,49 +13401,267 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Steam gatte as above. Slice.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
-    <row r="23" ht="42" customHeight="1">
+    <row r="23" ht="36" customHeight="1">
       <c r="A23" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B23" s="30" t="inlineStr">
         <is>
-          <t>Whisk yogurt with spices. Temper cumin hing. Add yogurt on low, then gatte. Simmer.</t>
+          <t>Cut vegetables to even size so they cook together.</t>
         </is>
       </c>
       <c r="C23" s="31" t="n"/>
       <c r="D23" s="31" t="n"/>
     </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Steam gatte as above. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Slice. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Whisk yogurt with spices. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Temper cumin hing. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Add yogurt on low, then gatte. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Simmer. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="n"/>
+      <c r="D33" s="31" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>kcal 503  ·  Protein 29 g  ·  Carbs 73 g  ·  Fat 9 g  ·  Fibre 13 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="48" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+    </row>
+    <row r="40" ht="72" customHeight="1">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>For Gatte ki sabzi (no onion garlic): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Bring yogurt to a simmer gently and stir; a rolling boil can split it. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B41" s="52" t="n"/>
+      <c r="C41" s="52" t="n"/>
+      <c r="D41" s="52" t="n"/>
+    </row>
+    <row r="42" ht="64" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B42" s="50" t="n"/>
+      <c r="C42" s="50" t="n"/>
+      <c r="D42" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="35">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9858,7 +13675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9870,7 +13687,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Ker sangri (desert beans, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Ker sangri (desert beans, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9880,7 +13697,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajasthan kitchen  ·  Main  ·  Marwari, Mewari and Jain vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Rajasthan  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9900,44 +13717,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 15 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -10139,13 +13956,13 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Boil soaked ker-sangri till tender. Drain.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
@@ -10157,32 +13974,250 @@
       </c>
       <c r="B24" s="30" t="inlineStr">
         <is>
-          <t>Temper spices, tomato. Add beans. Cook dry-ish. Finish amchur.</t>
+          <t>Cut vegetables to even size so they cook together.</t>
         </is>
       </c>
       <c r="C24" s="31" t="n"/>
       <c r="D24" s="31" t="n"/>
     </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Boil soaked ker-sangri till tender. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Drain. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Temper spices, tomato. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Add beans. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Cook dry-ish. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Finish amchur. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="B33" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="49" t="n"/>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C34" s="31" t="n"/>
+      <c r="D34" s="31" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="n"/>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="22" t="n"/>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>kcal 49  ·  Protein 2 g  ·  Carbs 8 g  ·  Fat 2 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+    </row>
+    <row r="39" ht="48" customHeight="1">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+    </row>
+    <row r="41" ht="72" customHeight="1">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>For Ker sangri (desert beans, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B41" s="26" t="n"/>
+      <c r="C41" s="26" t="n"/>
+      <c r="D41" s="26" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B42" s="52" t="n"/>
+      <c r="C42" s="52" t="n"/>
+      <c r="D42" s="52" t="n"/>
+    </row>
+    <row r="43" ht="64" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B43" s="50" t="n"/>
+      <c r="C43" s="50" t="n"/>
+      <c r="D43" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="36">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
